--- a/Unity/Assets/Config/Excel/Monster@怪物配置/MonsterConfig.xlsx
+++ b/Unity/Assets/Config/Excel/Monster@怪物配置/MonsterConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17775"/>
   </bookViews>
   <sheets>
     <sheet name="MonsterConfig" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="30">
   <si>
     <t>#</t>
   </si>
@@ -38,12 +38,18 @@
     <t>Note说明</t>
   </si>
   <si>
+    <t>名称</t>
+  </si>
+  <si>
     <t>Asset资源名称</t>
   </si>
   <si>
     <t>Note</t>
   </si>
   <si>
+    <t>Name</t>
+  </si>
+  <si>
     <t>AssetName</t>
   </si>
   <si>
@@ -53,31 +59,61 @@
     <t>string</t>
   </si>
   <si>
+    <t>Hero1</t>
+  </si>
+  <si>
     <t>Monster_001</t>
   </si>
   <si>
+    <t>Hero2</t>
+  </si>
+  <si>
     <t>Monster_002</t>
   </si>
   <si>
+    <t>Hero3</t>
+  </si>
+  <si>
     <t>Monster_003</t>
   </si>
   <si>
+    <t>Hero4</t>
+  </si>
+  <si>
     <t>Monster_004</t>
   </si>
   <si>
+    <t>Hero5</t>
+  </si>
+  <si>
     <t>Monster_005</t>
   </si>
   <si>
+    <t>Hero6</t>
+  </si>
+  <si>
     <t>Monster_006</t>
   </si>
   <si>
+    <t>Hero7</t>
+  </si>
+  <si>
     <t>Monster_007</t>
   </si>
   <si>
+    <t>Hero8</t>
+  </si>
+  <si>
     <t>Monster_008</t>
   </si>
   <si>
+    <t>Hero9</t>
+  </si>
+  <si>
     <t>Monster_009</t>
+  </si>
+  <si>
+    <t>Hero10</t>
   </si>
   <si>
     <t>Monster_010</t>
@@ -1075,23 +1111,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C2:E15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
+  <dimension ref="C2:F15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.75" style="2" customWidth="1"/>
     <col min="3" max="3" width="12.625" style="2" customWidth="1"/>
-    <col min="4" max="5" width="15.125" style="2" customWidth="1"/>
-    <col min="6" max="16381" width="9" style="2"/>
-    <col min="16384" max="16384" width="9" style="2"/>
+    <col min="4" max="6" width="15.125" style="2" customWidth="1"/>
+    <col min="7" max="16382" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:5">
+    <row r="2" spans="4:4">
       <c r="D2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="3:5">
+    <row r="3" spans="3:6">
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
@@ -1101,111 +1136,150 @@
       <c r="E3" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="3:5">
+      <c r="F3" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="3:6">
       <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="3:5">
+        <v>6</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="3:6">
       <c r="C5" s="3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="3:5">
+        <v>9</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="3:6">
       <c r="C6" s="1">
         <v>1</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="3:5">
+        <v>10</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="3:6">
       <c r="C7" s="1">
         <v>2</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" spans="3:5">
+        <v>12</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="3:6">
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" spans="3:5">
+        <v>14</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="3:6">
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="3:5">
+        <v>16</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="3:6">
       <c r="C10" s="1">
         <v>5</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="3:5">
+        <v>18</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="3:6">
       <c r="C11" s="1">
         <v>6</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="3:5">
+        <v>20</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="3:6">
       <c r="C12" s="1">
         <v>7</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="3:5">
+        <v>22</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="3:6">
       <c r="C13" s="1">
         <v>8</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="3:5">
+        <v>24</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="3:6">
       <c r="C14" s="1">
         <v>9</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="3:5">
+        <v>26</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="3:6">
       <c r="C15" s="1">
         <v>10</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>17</v>
+        <v>28</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
